--- a/new/260808.xlsx
+++ b/new/260808.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8715CC96-EDEF-4607-8FC4-449F37259599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72B31C2-ABAF-4065-9FB8-C1DD1AC30875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
 Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
@@ -189,104 +190,6 @@
 In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
 Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
 Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wie ist Ihre Bilanz ein Jahr vor der Bundestagswahl?
-Scholz: Wir haben viele Erfolge durchsetzen können.
-Der wichtigste ist sicherlich die Einführung eines allgemeinen, gleichen, flächendeckenden Mindestlohns in Deutschland.
-Deutschland ist Nachzügler.
-Das gibt es in vielen, vielen vergleichbaren Ländern – jetzt haben wir das auch.
-Und es gibt Verbesserungen etwa im Bereich der Sicherheit von Arbeitsplätzen und von Arbeitnehmerrechten, bei der Leiharbeit, bei Werkverträgen sind wir an der Sache dran.
-Das ist alles wichtig und eine gute Leistungsbilanz.
-Detjen: Das sah ja schon am Anfang dieser Großen Koalition so aus.
-In den ersten Monaten hat die SPD ein Projekt nach dem anderen durchgekriegt.
-Es wirkte so – so haben auch wir in den Medien das beschrieben –, als diktiert die SPD die Agenda dieser Großen Koalition.
-Das flachte dann etwas ab und vor allen Dingen hat es sich in den Umfragewerten nie richtig niedergeschlagen.
-Woran liegt das?
-Scholz: Erstmal ist es wichtig, dass man gute Arbeit leistet und es ist nicht schlecht, dass alle das immerhin attestieren.
-Das ist ja eine gute Empfehlung, wenn es zu Wahlen geht.
-Und im Übrigen geht es bei Wahlen darum, dass wir die Bürgerinnen und Bürger davon überzeugen, dass man uns auch das Mandat, die Regierung zuführen, anvertrauen kann.
-Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
-Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
-Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, Torsten Albig, der Ministerpräsident von Schleswig-Holstein, noch in Frage gestellt, ob die SPD 2017 überhaupt einen eigenen Kanzlerkandidaten aufstellen sollte.
-Das war vor der Flüchtlingskrise.
-Wie sieht das heute aus?
-Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
-Wir wollen den Kanzler dieser Republik stellen.
-Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Und Sie, das haben Sie immer wieder erklärt, sind dafür, dass Sigmar Gabriel das sein soll?
-Scholz: Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat, sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
-Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
-Scholz: Das ist ja nichts Schlechtes, dass man das allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
-Trotzdem gilt, der Parteivorsitzende wird einen Vorschlag machen.
-Und ich wiederhole es nochmal: Ein Parteivorsitzender ist immer ein guter Kandidat.
-Detjen: Wo ist die Linkspartei zurzeit für Sie ein Regierungspartner der SPD, ein guter Regierungspartner?
-wo in den Ländern?
-Auf Bundesebene auch?
-Scholz: Die Partei Die Linke vertritt politische Positionen im Hinblick auf die Entwicklung unseres Landes, auf die Entwicklung Europas, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
-Deshalb kann man beim Blick auf die Partei Die Linke große Skepsis haben, dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
-Ich halte das nicht für möglich.
-Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
-Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
-Ist das für Sie erstrebenswert?
-Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
-Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
-Und das sollte auch im Vordergrund der Bemühungen stehen.
-Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
-Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
-Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
-Scholz: Das glaube ich schon.
-Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
-Was ist da schiefgelaufen?
-Scholz: Weiß ich nicht.
-Ich kenne mich vor Ort nicht genug aus.
-Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
-Und das muss jetzt auch schnell in Ordnung gebracht werden.
-Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
-Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
-Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-Scholz: Letzteres ganz bestimmt nicht.
-Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
-Das kann ich mir auch nicht so richtig erklären.
-Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
-Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD. """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Dafür sorgen, dass es eine gute Zukunft gibt"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Warum ist die für Sie die """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Partei der schlechten Laune"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
-Und über sowas muss man diskutieren.
-Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
-Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -588,6 +491,100 @@
 Im April haben Sie fünf Personen festnehmen lassen wegen des Verdachts der Mitgliedschaft in einer rechtsterroristischen Vereinigung.
 Dieser  Gruppe Freital.
 rechnen Sie auch noch weitere Personen hinzu.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
+Wir wollen den Kanzler dieser Republik stellen.
+Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Und Sie, das haben Sie immer wieder erklärt, sind dafür, dass Sigmar Gabriel das sein soll?
+Scholz: Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat, sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
+Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
+Scholz: Das ist ja nichts Schlechtes, dass man das allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
+Trotzdem gilt, der Parteivorsitzende wird einen Vorschlag machen.
+Und ich wiederhole es nochmal: Ein Parteivorsitzender ist immer ein guter Kandidat.
+Detjen: Wo ist die Linkspartei zurzeit für Sie ein Regierungspartner der SPD, ein guter Regierungspartner?
+wo in den Ländern?
+Auf Bundesebene auch?
+Scholz: Die Partei Die Linke vertritt politische Positionen im Hinblick auf die Entwicklung unseres Landes, auf die Entwicklung Europas, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
+Deshalb kann man beim Blick auf die Partei Die Linke große Skepsis haben, dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
+Ich halte das nicht für möglich.
+Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
+Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
+Ist das für Sie erstrebenswert?
+Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
+Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
+Und das sollte auch im Vordergrund der Bemühungen stehen.
+Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
+Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
+Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
+Scholz: Das glaube ich schon.
+Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
+Was ist da schiefgelaufen?
+Scholz: Weiß ich nicht.
+Ich kenne mich vor Ort nicht genug aus.
+Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
+Und das muss jetzt auch schnell in Ordnung gebracht werden.
+Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
+Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
+Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
+Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
+Scholz: Letzteres ganz bestimmt nicht.
+Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
+Das kann ich mir auch nicht so richtig erklären.
+Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
+Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
+Das bezog sich nicht auf die SPD, richtig?
+Scholz: Klar, das bezog sich auf die AfD. """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Dafür sorgen, dass es eine gute Zukunft gibt"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Warum ist die für Sie die """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Partei der schlechten Laune"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
+Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
+Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
+Was machen wir mit unseren öffentlichen Haushalten?
+Wie statten wir die Bundeswehr und unsere Polizei gut aus?
+Was machen wir, um die Bildung zu verbessern an den Schulen?
+Wie setzen wir Forschung und Universitäten auf die richtige Spur?
+Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
+Und über sowas muss man diskutieren.
+Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
+Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
+Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
+Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
+Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
+Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
+Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
+Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
+Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
+Das muss das Ergebnis des letzten Jahres sein.
+Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
+Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
+Detjen: Nochmal der Blick konkret auf Hamburg.
+Was haben Sie geschafft in diesem Jahr?
+Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
+'.
+Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
+Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
+Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
+Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
+Detjen: Und vieles ist noch zu tun.
+Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
+Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
+Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
+Detjen: Herr Bürgermeister, vielen Dank.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie ist Ihre Bilanz 
+Deutschland ist Nachzügler.
+Das gibt es in vielen, vielen vergleichbaren Ländern – jetzt haben wir das auch.
+und von Arbeitnehmerrechten, bei der Leiharbeit.
+Detjen: Das sah ja schon am Anfang dieser Großen Koalition so aus.
+In den ersten Monaten hat die SPD ein Projekt nach dem anderen durchgekriegt.
+Es wirkte so – so haben auch wir in den Medien das beschrieben –, als diktiert die SPD die Agenda dieser Großen Koalition.
+Das flachte dann etwas ab und vor allen Dingen hat es sich in den Umfragewerten nie richtig niedergeschlagen.
+Woran liegt das?
+Scholz: die Regierung zuführen, anvertrauen kann.
+Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
+Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
+Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -924,7 +921,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +940,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -953,6 +950,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF1DD58-4669-43E0-839F-4C49A776A038}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.4140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -966,27 +982,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -995,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/new/260808.xlsx
+++ b/new/260808.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72B31C2-ABAF-4065-9FB8-C1DD1AC30875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7221F190-BF0B-4249-ADD4-01628A8091B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
 Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
@@ -118,78 +119,6 @@
 Das ist auch ein wichtiger Unterschied, der zu machen ist.
 Hahne: Herr Mattes, vielen Dank für das Gespräch.
 Mattes: Bitteschön.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
-Aber es wird auch darum gehen müssen, Investitionen in die Digitalisierung zu schaffen, die Infrastruktur zu verbessern.
-Nur wenn wir gute wirtschaftliche Rahmenbedingungen haben, dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben, auch besser Renten haben.
-Wir haben jetzt eine Rentenerhöhung gehabt, die hatten wir in den letzten 20 Jahren nicht so hoch, mit knapp sechs Prozent.
-Das, glaube ich, gehört auch dazu, dass wir in den nächsten zwölf Monaten auch darüber diskutieren müssen in Deutschland: Was ist notwendig, damit das Land erfolgreich bleibt.
-Das sind die beiden Dinge, mehr Sicherheit zu schaffen, aber auch den Erfolg der deutschen Wirtschaft, die Schaffung von Arbeitsplätzen zum Thema zu machen.
-Ich fände es jedenfalls gut, wenn es in einem Bundestagswahlkampf um die Zukunft unseres Landes ginge und nicht nur um die Frage, wer irgendwie die besten Personen aufstellt.
-Geers: Die SPD muss natürlich auch die Frage beantworten: Wie wird das bezahlt?
-Also, wenn ich jetzt überlege oder wenn ich jetzt zusammenzähle: Mehr innere Sicherheit, mehr äußere Sicherheit, Bekämpfung des Terrorismus, Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land, mehr Geld für Bildung, vielleicht auch mehr Geld für Wachstum in Europa nach einem möglichen Brexit, da kommt Vieles zusammen.
-Und dann muss natürlich auch die SPD Antwort geben darauf, dass es das alles nicht zum Nulltarif gibt.
-Also, woher kommt das Geld?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Formen legaler Steuervermeidung bekämpfen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Erstens haben wir das große Glück, dass wir in einer Phase leben, wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
-Wir wären nicht klug beraten, wenn wir die nicht investieren würden in Bildung und in Infrastruktur - das ist die Zukunft unseres Landes.
-Zweitens wird es auch darum gehen - Sie haben das Stichwort völlig zurecht genannt -, was machen wir eigentlich in Europa.
-In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, weil wir in Europa Steueroasen haben und dann gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
-Unser Land verliert nach Berechnungen der Europäischen Kommission in jedem Jahr 150 Milliarden Euro durch diese Form legaler Steuervermeidung - das ist die Hälfte des Bundeshaushaltes!
-Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
-Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber dass wir uns wenigstens darauf verständigen, was besteuern wir.
-Das muss Europa schaffen.
-Wenn nicht, werden die Menschen immer weniger bereit sein, sagen wir mal, in Europa etwas zu erkennen, was ihren Lebensinteressen entspricht.
-Und es kann nicht sein, dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
-Das ist auch ein großes europäisches Thema.
-Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es ist kein Ziel per se, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also, ich weiß nicht genau, warum man Spaß daran haben soll, Schulden zu machen, sondern das Schönste ist natürlich, wenn man keine macht.
-Und deswegen, es ist ja kein Ziel per se, Schulden zu machen.
-Ich glaube, dass die Frage, ob man sich verschuldet oder nicht, mit zwei zentralen Fragen zu tun hat.
-Erstens, sind es Daueraufgaben, für die man sich verschuldet, dann darf man das eigentlich nicht machen.
-Oder sind es Investitionen, die man tätigt, damit die Bedingungen gut werden in der Infrastruktur, in der Digitalisierung, dann darf man das natürlich, wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
-Und der Fehler der Politik der Vergangenheit ist in der Regel gewesen, dass sich gerade um die zweite Frage keiner Gedanken gemacht hat.
-Ich persönlich bin froh darüber, dass wir in einer Situation leben, in der wir das nicht müssen, in der wir ausgeglichene Haushalte haben.
-Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur, weil wir eine gut laufende Wirtschaft haben.
-Und das bedeutet: Wer das in Zukunft auch haben will, der muss die Bedingungen für erfolgreiche Wirtschaft in Deutschland gut halten.
-Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
-Geers: Als da wären?
-Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie junge Unternehmen haben, wo die Unternehmen investieren wollen.
-Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage, was können sie an kurzlebigen Wirtschaftsgütern von der Steuer absetzen, welche Vorschriften müssen sie einhalten, wenn sie ein junges Unternehmen gründen.
-Wir haben jetzt, Gott sei Dank, zwei Bürokratieentlastungsgesetze mit insgesamt mit mehr als zwei Milliarden Euro Entlastung gemacht.
-Aber ich sage Ihnen: Da ist noch mehr drin!
-Dann die Frage Fachkräfte, die Digitalisierung.
-Wir werden in Deutschland auf Sicht keine Chance haben, wirtschaftliche Erfolge zu haben, wenn wir nicht wesentlich besser werden bei der digitalen Infrastruktur.
-Wir haben jetzt ein Ziel von 50 Megabit pro Sekunde im Jahr 2018.
-Das ist in Ordnung, aber jeder weiß: Das ist viel zu wenig.
-Eigentlich muss Deutschland, muss sich Europa das Ziel setzen, im Jahr 2025 die beste digitale Infrastruktur der Welt zu haben – ohne das werden wir das nicht schaffen.
-Das sind Dinge, die als Voraussetzung geschaffen werden müssen, damit die Wirtschaft gut läuft.
-Geers: Würden Sie soweit gehen, Herr Gabriel, dass Sie sagen, mit Blick auch auf die aktuell ja eher günstige Lage, was die Finanzierungsmöglichkeiten des Staates betrifft – er zahlt ja so gut wie keine Zinsen derzeit, der Staat, Deutschland –, dass man diese Zeiten nutzen sollte möglicherweise, um auch für solche Projekt, die man ja definieren könnte als sinnvoll, zukunftsgewandt und, und, und, dass man sagt, für solche Projekte machen wir auch Schulden und haben dann eben jetzt die Möglichkeit, jetzt für vergleichsweise preiswertes Geld Zukunftsinvestitionen zu tätigen?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Für die Digitalisierung wäre ich dafür, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Alle auf der Welt sagen uns das. Alle. Es gibt nur einen, der anderer Meinung ist, das ist der Bundesfinanzminister.
-Weil alle Ökonomen sagen: 'Ihr seid ja verrückt, dass ihr eure Schulen und eure Infrastruktur verkommen lasst in einer Zeit, wo euch die Investitionen zur Sanierung von Infrastruktur und Schulen nichts kostet und in paar Jahren müsst ihr es dann doch machen und wenn ihr Pech habt, sind die Zinsen dann höher.
-' Es spricht viel dafür, für Investitionen in die Infrastruktur im Zweifel auch bereit zu sein, sich zu verschulden.
-Aber ich sage noch mal: Das kann kein Ziel an sich sein.
-Zurzeit haben wir mit Hilfe auch von Wolfgang Schäuble und der Bundesregierung insgesamt ja zum Beispiel die kommunale Investitionsmöglichkeit deutlich erhöht und mussten dafür überhaupt keine Schulden machen.
-Zweitens, wenn man das macht – zum Beispiel für die Digitalisierung wäre ich dafür, es zu tun –, dann muss man auch eine Vorstellung darüber haben, wie man das zurückzahlt.
-Ein Thema dabei ist – muss man auch offen sagen –, dass ich zum Beispiel glaube, dass es nicht in Ordnung ist, dass wir die Einkommen durch Arbeit stärker besteuern als die Einkommen die man hat, wenn man Aktien besitzt.
-Es kann ja nicht sein, dass einer, der arbeiten geht, höhere Steuern zahlt auf den gleichen Betrag, als jemand, der auf dem Sofa liegt und das über die Aktien bekommt.
-Das haben wir mal eingeführt, weil wir gehofft haben, dass die Steuerflucht nachlässt.
-Heute haben wir Datenaustausch, es gibt kein Bankgeheimnis mehr, wir können die Steuerhinterziehung anders bekämpfen.
-Geers: Also, Abgeltungssteuer abschaffen?
-Gabriel: Die Abgeltungssteuer ist der Fachbegriff dafür.
-Und das Geld, das wir dort bekommen, sollten wir ausschließlich in den Bildungsbereich stecken.
-Ein großes Schulsanierungsprogramm, Sanierung der Sportstätten, Einstellung von Sozialpädagogen in den Ganztagsschulen.
-Das wäre ein großes Programm, was auch mal zeigen würde: Bildung ist uns was wert!
-Geers: Sagt Sigmar Gabriel, der Vizekanzler, der SPD-Chef und der mögliche SPD-Kanzlerkandidat, der dabei bleibt, dass diese Entscheidung erst Anfang nächsten Jahres getroffen wird?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Erst mal sagen, was man will und dann eine Person bestimmen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Ich habe schon darauf gewartet, dass die Frage kommt.
-Geers: Ich stelle sie am Schluss.
-Gabriel: Ja, ist ja auch in Ordnung.
-Ich meine, ich will es einfach nur erklären.
-Wenn wir jetzt anfangen, Personal bei uns zu debattieren, können Sie als Journalisten überhaupt nicht anders, als nur darüber zu reden.
-In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
-Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
-Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -585,6 +514,76 @@
 Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
 Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
 Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>da kommt Vieles zusammen.
+Und dann muss natürlich auch die SPD Antwort geben darauf, dass es das alles nicht zum Nulltarif gibt.
+Also, woher kommt das Geld?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Formen legaler Steuervermeidung bekämpfen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Erstens haben wir das große Glück, dass wir in einer Phase leben, wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
+Wir wären nicht klug beraten, wenn wir die nicht investieren würden in Bildung und in Infrastruktur - das ist die Zukunft unseres Landes.
+Zweitens wird es auch darum gehen - Sie haben das Stichwort völlig zurecht genannt -, was machen wir eigentlich in Europa.
+In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, weil wir in Europa Steueroasen haben und dann gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
+Unser Land verliert nach Berechnungen der Europäischen Kommission in jedem Jahr 150 Milliarden Euro durch diese Form legaler Steuervermeidung - das ist die Hälfte des Bundeshaushaltes!
+Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
+Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber dass wir uns wenigstens darauf verständigen, was besteuern wir.
+Das muss Europa schaffen.
+Wenn nicht, werden die Menschen immer weniger bereit sein, sagen wir mal, in Europa etwas zu erkennen, was ihren Lebensinteressen entspricht.
+Und es kann nicht sein, dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
+Das ist auch ein großes europäisches Thema.
+Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es ist kein Ziel per se, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also, ich weiß nicht genau, warum man Spaß daran haben soll, Schulden zu machen, sondern das Schönste ist natürlich, wenn man keine macht.
+Und deswegen, es ist ja kein Ziel per se, Schulden zu machen.
+Ich glaube, dass die Frage, ob man sich verschuldet oder nicht, mit zwei zentralen Fragen zu tun hat.
+Erstens, sind es Daueraufgaben, für die man sich verschuldet, dann darf man das eigentlich nicht machen.
+Oder sind es Investitionen, die man tätigt, damit die Bedingungen gut werden in der Infrastruktur, in der Digitalisierung, dann darf man das natürlich, wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
+Und der Fehler der Politik der Vergangenheit ist in der Regel gewesen, dass sich gerade um die zweite Frage keiner Gedanken gemacht hat.
+Ich persönlich bin froh darüber, dass wir in einer Situation leben, in der wir das nicht müssen, in der wir ausgeglichene Haushalte haben.
+Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur, weil wir eine gut laufende Wirtschaft haben.
+Und das bedeutet: Wer das in Zukunft auch haben will, der muss die Bedingungen für erfolgreiche Wirtschaft in Deutschland gut halten.
+Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
+Geers: Als da wären?
+Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie junge Unternehmen haben, wo die Unternehmen investieren wollen.
+Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage, was können sie an kurzlebigen Wirtschaftsgütern von der Steuer absetzen, welche Vorschriften müssen sie einhalten, wenn sie ein junges Unternehmen gründen.
+Wir haben jetzt, Gott sei Dank, zwei Bürokratieentlastungsgesetze mit insgesamt mit mehr als zwei Milliarden Euro Entlastung gemacht.
+Aber ich sage Ihnen: Da ist noch mehr drin!
+Dann die Frage Fachkräfte, die Digitalisierung.
+Wir werden in Deutschland auf Sicht keine Chance haben, wirtschaftliche Erfolge zu haben, wenn wir nicht wesentlich besser werden bei der digitalen Infrastruktur.
+Wir haben jetzt ein Ziel von 50 Megabit pro Sekunde im Jahr 2018.
+Das ist in Ordnung, aber jeder weiß: Das ist viel zu wenig.
+Eigentlich muss Deutschland, muss sich Europa das Ziel setzen, im Jahr 2025 die beste digitale Infrastruktur der Welt zu haben – ohne das werden wir das nicht schaffen.
+Das sind Dinge, die als Voraussetzung geschaffen werden müssen, damit die Wirtschaft gut läuft.
+Geers: Würden Sie soweit gehen, Herr Gabriel, dass Sie sagen, mit Blick auch auf die aktuell ja eher günstige Lage, was die Finanzierungsmöglichkeiten des Staates betrifft – er zahlt ja so gut wie keine Zinsen derzeit, der Staat, Deutschland –, dass man diese Zeiten nutzen sollte möglicherweise, um auch für solche Projekt, die man ja definieren könnte als sinnvoll, zukunftsgewandt und, und, und, dass man sagt, für solche Projekte machen wir auch Schulden und haben dann eben jetzt die Möglichkeit, jetzt für vergleichsweise preiswertes Geld Zukunftsinvestitionen zu tätigen?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Für die Digitalisierung wäre ich dafür, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Alle auf der Welt sagen uns das. Alle. Es gibt nur einen, der anderer Meinung ist, das ist der Bundesfinanzminister.
+Weil alle Ökonomen sagen: 'Ihr seid ja verrückt, dass ihr eure Schulen und eure Infrastruktur verkommen lasst in einer Zeit, wo euch die Investitionen zur Sanierung von Infrastruktur und Schulen nichts kostet und in paar Jahren müsst ihr es dann doch machen und wenn ihr Pech habt, sind die Zinsen dann höher.
+' Es spricht viel dafür, für Investitionen in die Infrastruktur im Zweifel auch bereit zu sein, sich zu verschulden.
+Aber ich sage noch mal: Das kann kein Ziel an sich sein.
+Zurzeit haben wir mit Hilfe auch von Wolfgang Schäuble und der Bundesregierung insgesamt ja zum Beispiel die kommunale Investitionsmöglichkeit deutlich erhöht und mussten dafür überhaupt keine Schulden machen.
+Zweitens, wenn man das macht – zum Beispiel für die Digitalisierung wäre ich dafür, es zu tun –, dann muss man auch eine Vorstellung darüber haben, wie man das zurückzahlt.
+Ein Thema dabei ist – muss man auch offen sagen –, dass ich zum Beispiel glaube, dass es nicht in Ordnung ist, dass wir die Einkommen durch Arbeit stärker besteuern als die Einkommen die man hat, wenn man Aktien besitzt.
+Es kann ja nicht sein, dass einer, der arbeiten geht, höhere Steuern zahlt auf den gleichen Betrag, als jemand, der auf dem Sofa liegt und das über die Aktien bekommt.
+Das haben wir mal eingeführt, weil wir gehofft haben, dass die Steuerflucht nachlässt.
+Heute haben wir Datenaustausch, es gibt kein Bankgeheimnis mehr, wir können die Steuerhinterziehung anders bekämpfen.
+Geers: Also, Abgeltungssteuer abschaffen?
+Gabriel: Die Abgeltungssteuer ist der Fachbegriff dafür.
+Und das Geld, das wir dort bekommen, sollten wir ausschließlich in den Bildungsbereich stecken.
+Ein großes Schulsanierungsprogramm, Sanierung der Sportstätten, Einstellung von Sozialpädagogen in den Ganztagsschulen.
+Das wäre ein großes Programm, was auch mal zeigen würde: Bildung ist uns was wert!
+Geers: Sagt Sigmar Gabriel, der Vizekanzler, der SPD-Chef und der mögliche SPD-Kanzlerkandidat, der dabei bleibt, dass diese Entscheidung erst Anfang nächsten Jahres getroffen wird?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Erst mal sagen, was man will und dann eine Person bestimmen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Ich habe schon darauf gewartet, dass die Frage kommt.
+Geers: Ich stelle sie am Schluss.
+Gabriel: Ja, ist ja auch in Ordnung.
+Ich meine, ich will es einfach nur erklären.
+Wenn wir jetzt anfangen, Personal bei uns zu debattieren, können Sie als Journalisten überhaupt nicht anders, als nur darüber zu reden.
+In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
+Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
+Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
+Aber dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben.
+Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -921,7 +920,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +939,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +958,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -969,6 +968,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321AC828-CA52-4D30-9A36-854D6436B639}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="182" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -982,36 +1000,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
